--- a/sync/config_setting.xlsx
+++ b/sync/config_setting.xlsx
@@ -4,19 +4,18 @@
   <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9302"/>
   <workbookPr defaultThemeVersion="124226"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="90" windowWidth="17235" windowHeight="2655" activeTab="2"/>
+    <workbookView xWindow="0" yWindow="90" windowWidth="17235" windowHeight="2655"/>
   </bookViews>
   <sheets>
     <sheet name="Proyek" sheetId="1" r:id="rId1"/>
     <sheet name="HPS" sheetId="2" r:id="rId2"/>
-    <sheet name="Rekap" sheetId="3" r:id="rId3"/>
   </sheets>
   <calcPr calcId="144525"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="42" uniqueCount="30">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="22" uniqueCount="21">
   <si>
     <t>Nama Proyek</t>
   </si>
@@ -24,6 +23,9 @@
     <t>URL</t>
   </si>
   <si>
+    <t>LPD UAE</t>
+  </si>
+  <si>
     <t>https://docs.google.com/spreadsheets/d/19qiMBb1b7qmeRXkFNTbh-eKtVEKDUTgshloa116HQ48/export?format=csv&amp;gid=1797511471</t>
   </si>
   <si>
@@ -33,18 +35,30 @@
     <t>https://docs.google.com/spreadsheets/d/1uv2D4ECJ0z-NWP8byzXTkkM17MKD6f0r-RCtKjpG5Hs/export?format=csv&amp;gid=678820326</t>
   </si>
   <si>
+    <t>FRIGATE 140 M</t>
+  </si>
+  <si>
     <t>GEOMARIN V</t>
   </si>
   <si>
     <t>KSOT</t>
   </si>
   <si>
+    <t>LD PN 124 M</t>
+  </si>
+  <si>
+    <t>LCU LD PN 124 M</t>
+  </si>
+  <si>
     <t>KSSR 18 M</t>
   </si>
   <si>
     <t>KSR 20 M</t>
   </si>
   <si>
+    <t>https://docs.google.com/spreadsheets/d/1QCjqjtzLXSlrIebF0slfl-spm_txCqMb5FR2ecQAnoM/export?format=csv&amp;gid=102037561</t>
+  </si>
+  <si>
     <t>https://docs.google.com/spreadsheets/d/1CBL96MejQnswfg_sLIkwkK9K594S9hDWoSGDBIeIBNo/export?format=csv&amp;gid=1941501876</t>
   </si>
   <si>
@@ -64,48 +78,6 @@
   </si>
   <si>
     <t>https://docs.google.com/spreadsheets/d/1l0ZoTCctHrmkruIkC4Gk1NtoqsugMVGABrsf3yb6PHo/export?format=csv&amp;gid=556011475</t>
-  </si>
-  <si>
-    <t>FRIGATE MERAH PUTIH 140 M</t>
-  </si>
-  <si>
-    <t>LD PHILLIPINE NAVY 124 M</t>
-  </si>
-  <si>
-    <t>LCU LD PHILLIPINE 124 M</t>
-  </si>
-  <si>
-    <t>LPD UAE 163 M</t>
-  </si>
-  <si>
-    <t>https://docs.google.com/spreadsheets/d/1OLxSphh-jiqmUGIHE9QSXkRCVfwoVhkRsyP3InRzAgk/export?format=csv&amp;gid=1396918909</t>
-  </si>
-  <si>
-    <t>https://docs.google.com/spreadsheets/d/19qiMBb1b7qmeRXkFNTbh-eKtVEKDUTgshloa116HQ48/export?format=csv&amp;gid=980871639</t>
-  </si>
-  <si>
-    <t>https://docs.google.com/spreadsheets/d/1uv2D4ECJ0z-NWP8byzXTkkM17MKD6f0r-RCtKjpG5Hs/export?format=csv&amp;gid=58275935</t>
-  </si>
-  <si>
-    <t>https://docs.google.com/spreadsheets/d/1OLxSphh-jiqmUGIHE9QSXkRCVfwoVhkRsyP3InRzAgk/export?format=csv&amp;gid=991986513</t>
-  </si>
-  <si>
-    <t>https://docs.google.com/spreadsheets/d/1CBL96MejQnswfg_sLIkwkK9K594S9hDWoSGDBIeIBNo/export?format=csv&amp;gid=351920294</t>
-  </si>
-  <si>
-    <t>https://docs.google.com/spreadsheets/d/1l0ZoTCctHrmkruIkC4Gk1NtoqsugMVGABrsf3yb6PHo/export?format=csv&amp;gid=1764284934</t>
-  </si>
-  <si>
-    <t>https://docs.google.com/spreadsheets/d/1ea2z7gEfavWoxZp9nBTc19A2PSq_GjkXP11tKvpAMfo/export?format=csv&amp;gid=1746645219</t>
-  </si>
-  <si>
-    <t>https://docs.google.com/spreadsheets/d/1jGNHh9HhSrPlEv7JZvtW8ToMU2ADrT0yE87tk9E53zY/export?format=csv&amp;gid=1820212871</t>
-  </si>
-  <si>
-    <t>https://docs.google.com/spreadsheets/d/1eTO-dvVd3psdP4mFQc2ZQW_Z-lyooCb2TVjR4mYTbDw/export?format=csv&amp;gid=861187807</t>
-  </si>
-  <si>
-    <t>https://docs.google.com/spreadsheets/d/16rrjyU60BmzRIYFL3I1WRLkw_AfJPUwi8vZiJx2LYCg/export?format=csv&amp;gid=226364805</t>
   </si>
 </sst>
 </file>
@@ -514,78 +486,75 @@
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
-        <v>19</v>
+        <v>2</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>20</v>
+        <v>13</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>9</v>
+        <v>14</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>15</v>
+        <v>20</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B7" s="3" t="s">
         <v>17</v>
-      </c>
-      <c r="B7" s="3" t="s">
-        <v>12</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>10</v>
+        <v>15</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>11</v>
+        <v>16</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="B13" s="3"/>
+        <v>18</v>
+      </c>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B14" s="3"/>
@@ -594,15 +563,16 @@
   <hyperlinks>
     <hyperlink ref="B2" r:id="rId1"/>
     <hyperlink ref="B3" r:id="rId2"/>
-    <hyperlink ref="B5" r:id="rId3"/>
-    <hyperlink ref="B6" r:id="rId4"/>
-    <hyperlink ref="B7" r:id="rId5"/>
-    <hyperlink ref="B8" r:id="rId6"/>
-    <hyperlink ref="B9" r:id="rId7"/>
-    <hyperlink ref="B10" r:id="rId8"/>
+    <hyperlink ref="B4" r:id="rId3"/>
+    <hyperlink ref="B5" r:id="rId4"/>
+    <hyperlink ref="B6" r:id="rId5"/>
+    <hyperlink ref="B7" r:id="rId6"/>
+    <hyperlink ref="B8" r:id="rId7"/>
+    <hyperlink ref="B9" r:id="rId8"/>
+    <hyperlink ref="B10" r:id="rId9"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" r:id="rId9"/>
+  <pageSetup orientation="portrait" r:id="rId10"/>
 </worksheet>
 </file>
 
@@ -621,7 +591,7 @@
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" s="3" t="s">
-        <v>14</v>
+        <v>19</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
@@ -640,115 +610,4 @@
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:B14"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="1" max="1" width="54.42578125" style="1" customWidth="1"/>
-    <col min="2" max="2" width="169.140625" style="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A1" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="2" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A2" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="B2" s="3" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A3" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="B3" s="3" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A4" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="B4" s="3" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A5" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="B5" s="3" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A6" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="B6" s="3" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A7" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="B7" s="3" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A8" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="B8" s="3" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A9" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="B9" s="3" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A10" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="B10" s="3" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="B13" s="3"/>
-    </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="B14" s="3"/>
-    </row>
-  </sheetData>
-  <hyperlinks>
-    <hyperlink ref="B2" r:id="rId1"/>
-    <hyperlink ref="B3" r:id="rId2"/>
-    <hyperlink ref="B5" r:id="rId3"/>
-    <hyperlink ref="B6" r:id="rId4"/>
-    <hyperlink ref="B7" r:id="rId5"/>
-    <hyperlink ref="B8" r:id="rId6"/>
-    <hyperlink ref="B9" r:id="rId7"/>
-    <hyperlink ref="B10" r:id="rId8"/>
-    <hyperlink ref="B4" r:id="rId9"/>
-  </hyperlinks>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
 </file>
--- a/sync/config_setting.xlsx
+++ b/sync/config_setting.xlsx
@@ -4,18 +4,19 @@
   <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9302"/>
   <workbookPr defaultThemeVersion="124226"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="90" windowWidth="17235" windowHeight="2655"/>
+    <workbookView xWindow="0" yWindow="90" windowWidth="17235" windowHeight="2655" activeTab="2"/>
   </bookViews>
   <sheets>
     <sheet name="Proyek" sheetId="1" r:id="rId1"/>
     <sheet name="HPS" sheetId="2" r:id="rId2"/>
+    <sheet name="Rekap" sheetId="3" r:id="rId3"/>
   </sheets>
   <calcPr calcId="144525"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="22" uniqueCount="21">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="42" uniqueCount="30">
   <si>
     <t>Nama Proyek</t>
   </si>
@@ -23,9 +24,6 @@
     <t>URL</t>
   </si>
   <si>
-    <t>LPD UAE</t>
-  </si>
-  <si>
     <t>https://docs.google.com/spreadsheets/d/19qiMBb1b7qmeRXkFNTbh-eKtVEKDUTgshloa116HQ48/export?format=csv&amp;gid=1797511471</t>
   </si>
   <si>
@@ -35,30 +33,18 @@
     <t>https://docs.google.com/spreadsheets/d/1uv2D4ECJ0z-NWP8byzXTkkM17MKD6f0r-RCtKjpG5Hs/export?format=csv&amp;gid=678820326</t>
   </si>
   <si>
-    <t>FRIGATE 140 M</t>
-  </si>
-  <si>
     <t>GEOMARIN V</t>
   </si>
   <si>
     <t>KSOT</t>
   </si>
   <si>
-    <t>LD PN 124 M</t>
-  </si>
-  <si>
-    <t>LCU LD PN 124 M</t>
-  </si>
-  <si>
     <t>KSSR 18 M</t>
   </si>
   <si>
     <t>KSR 20 M</t>
   </si>
   <si>
-    <t>https://docs.google.com/spreadsheets/d/1QCjqjtzLXSlrIebF0slfl-spm_txCqMb5FR2ecQAnoM/export?format=csv&amp;gid=102037561</t>
-  </si>
-  <si>
     <t>https://docs.google.com/spreadsheets/d/1CBL96MejQnswfg_sLIkwkK9K594S9hDWoSGDBIeIBNo/export?format=csv&amp;gid=1941501876</t>
   </si>
   <si>
@@ -78,6 +64,48 @@
   </si>
   <si>
     <t>https://docs.google.com/spreadsheets/d/1l0ZoTCctHrmkruIkC4Gk1NtoqsugMVGABrsf3yb6PHo/export?format=csv&amp;gid=556011475</t>
+  </si>
+  <si>
+    <t>FRIGATE MERAH PUTIH 140 M</t>
+  </si>
+  <si>
+    <t>LD PHILLIPINE NAVY 124 M</t>
+  </si>
+  <si>
+    <t>LCU LD PHILLIPINE 124 M</t>
+  </si>
+  <si>
+    <t>LPD UAE 163 M</t>
+  </si>
+  <si>
+    <t>https://docs.google.com/spreadsheets/d/1OLxSphh-jiqmUGIHE9QSXkRCVfwoVhkRsyP3InRzAgk/export?format=csv&amp;gid=1396918909</t>
+  </si>
+  <si>
+    <t>https://docs.google.com/spreadsheets/d/19qiMBb1b7qmeRXkFNTbh-eKtVEKDUTgshloa116HQ48/export?format=csv&amp;gid=980871639</t>
+  </si>
+  <si>
+    <t>https://docs.google.com/spreadsheets/d/1uv2D4ECJ0z-NWP8byzXTkkM17MKD6f0r-RCtKjpG5Hs/export?format=csv&amp;gid=58275935</t>
+  </si>
+  <si>
+    <t>https://docs.google.com/spreadsheets/d/1OLxSphh-jiqmUGIHE9QSXkRCVfwoVhkRsyP3InRzAgk/export?format=csv&amp;gid=991986513</t>
+  </si>
+  <si>
+    <t>https://docs.google.com/spreadsheets/d/1CBL96MejQnswfg_sLIkwkK9K594S9hDWoSGDBIeIBNo/export?format=csv&amp;gid=351920294</t>
+  </si>
+  <si>
+    <t>https://docs.google.com/spreadsheets/d/1l0ZoTCctHrmkruIkC4Gk1NtoqsugMVGABrsf3yb6PHo/export?format=csv&amp;gid=1764284934</t>
+  </si>
+  <si>
+    <t>https://docs.google.com/spreadsheets/d/1ea2z7gEfavWoxZp9nBTc19A2PSq_GjkXP11tKvpAMfo/export?format=csv&amp;gid=1746645219</t>
+  </si>
+  <si>
+    <t>https://docs.google.com/spreadsheets/d/1jGNHh9HhSrPlEv7JZvtW8ToMU2ADrT0yE87tk9E53zY/export?format=csv&amp;gid=1820212871</t>
+  </si>
+  <si>
+    <t>https://docs.google.com/spreadsheets/d/1eTO-dvVd3psdP4mFQc2ZQW_Z-lyooCb2TVjR4mYTbDw/export?format=csv&amp;gid=861187807</t>
+  </si>
+  <si>
+    <t>https://docs.google.com/spreadsheets/d/16rrjyU60BmzRIYFL3I1WRLkw_AfJPUwi8vZiJx2LYCg/export?format=csv&amp;gid=226364805</t>
   </si>
 </sst>
 </file>
@@ -486,75 +514,78 @@
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="B2" s="3" t="s">
         <v>2</v>
-      </c>
-      <c r="B2" s="3" t="s">
-        <v>3</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B3" s="3" t="s">
         <v>4</v>
-      </c>
-      <c r="B3" s="3" t="s">
-        <v>5</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>13</v>
+        <v>20</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>14</v>
+        <v>9</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>20</v>
+        <v>15</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
-        <v>9</v>
+        <v>17</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>17</v>
+        <v>12</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="B8" s="3" t="s">
         <v>10</v>
-      </c>
-      <c r="B8" s="3" t="s">
-        <v>15</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="B9" s="3" t="s">
         <v>11</v>
-      </c>
-      <c r="B9" s="3" t="s">
-        <v>16</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>18</v>
-      </c>
+        <v>13</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B13" s="3"/>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B14" s="3"/>
@@ -563,16 +594,15 @@
   <hyperlinks>
     <hyperlink ref="B2" r:id="rId1"/>
     <hyperlink ref="B3" r:id="rId2"/>
-    <hyperlink ref="B4" r:id="rId3"/>
-    <hyperlink ref="B5" r:id="rId4"/>
-    <hyperlink ref="B6" r:id="rId5"/>
-    <hyperlink ref="B7" r:id="rId6"/>
-    <hyperlink ref="B8" r:id="rId7"/>
-    <hyperlink ref="B9" r:id="rId8"/>
-    <hyperlink ref="B10" r:id="rId9"/>
+    <hyperlink ref="B5" r:id="rId3"/>
+    <hyperlink ref="B6" r:id="rId4"/>
+    <hyperlink ref="B7" r:id="rId5"/>
+    <hyperlink ref="B8" r:id="rId6"/>
+    <hyperlink ref="B9" r:id="rId7"/>
+    <hyperlink ref="B10" r:id="rId8"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" r:id="rId10"/>
+  <pageSetup orientation="portrait" r:id="rId9"/>
 </worksheet>
 </file>
 
@@ -591,7 +621,7 @@
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" s="3" t="s">
-        <v>19</v>
+        <v>14</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
@@ -610,4 +640,115 @@
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:B14"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="54.42578125" style="1" customWidth="1"/>
+    <col min="2" max="2" width="169.140625" style="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A1" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A2" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="B2" s="3" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A3" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B3" s="3" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A4" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="B4" s="3" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A5" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B5" s="3" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A6" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B6" s="3" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A7" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="B7" s="3" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A8" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="B8" s="3" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A9" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="B9" s="3" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A10" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B10" s="3" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B13" s="3"/>
+    </row>
+    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B14" s="3"/>
+    </row>
+  </sheetData>
+  <hyperlinks>
+    <hyperlink ref="B2" r:id="rId1"/>
+    <hyperlink ref="B3" r:id="rId2"/>
+    <hyperlink ref="B5" r:id="rId3"/>
+    <hyperlink ref="B6" r:id="rId4"/>
+    <hyperlink ref="B7" r:id="rId5"/>
+    <hyperlink ref="B8" r:id="rId6"/>
+    <hyperlink ref="B9" r:id="rId7"/>
+    <hyperlink ref="B10" r:id="rId8"/>
+    <hyperlink ref="B4" r:id="rId9"/>
+  </hyperlinks>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>